--- a/templates/Mau_Nhap_Danh_Sach_Phong.xlsx
+++ b/templates/Mau_Nhap_Danh_Sach_Phong.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Danh sách phòng" sheetId="1" r:id="R800e709e2fb34377"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hướng dẫn" sheetId="2" r:id="R534ef0d645ad4070"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Danh sách phòng" sheetId="1" r:id="R833ee80da67548cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hướng dẫn" sheetId="2" r:id="Rfc6d3ef3af784f27"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -206,8 +206,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="RoomImportTemplate" displayName="RoomImportTemplate" ref="A1:X2" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="24">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="RoomImportTemplate" displayName="RoomImportTemplate" ref="A1:Y2" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="25">
     <x:tableColumn id="1" name="Địa chỉ"/>
     <x:tableColumn id="2" name="Giá thuê"/>
     <x:tableColumn id="3" name="Tên phòng"/>
@@ -232,6 +232,7 @@
     <x:tableColumn id="22" name="Ngày có thể vào ở"/>
     <x:tableColumn id="23" name="Trạng thái"/>
     <x:tableColumn id="24" name="SĐT chủ nhà"/>
+    <x:tableColumn id="25" name="Ở chung với chủ nhà"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -459,6 +460,7 @@
     <x:col min="22" max="22" width="16" hidden="0" customWidth="1"/>
     <x:col min="23" max="23" width="18" hidden="0" customWidth="1"/>
     <x:col min="24" max="24" width="18" hidden="0" customWidth="1"/>
+    <x:col min="25" max="25" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="44" customHeight="1">
@@ -534,6 +536,9 @@
       <x:c r="X1" s="14" t="str">
         <x:v>SĐT chủ nhà</x:v>
       </x:c>
+      <x:c r="Y1" t="str">
+        <x:v>Ở chung với chủ nhà</x:v>
+      </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="10" t="str">
@@ -606,6 +611,9 @@
       <x:c r="X2" s="13" t="str">
         <x:v>0901234567</x:v>
       </x:c>
+      <x:c r="Y2" t="str">
+        <x:v>Không</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="10"/>
@@ -632,6 +640,7 @@
       <x:c r="V3" s="12"/>
       <x:c r="W3" s="9"/>
       <x:c r="X3" s="13"/>
+      <x:c r="Y3"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="10"/>
@@ -658,6 +667,7 @@
       <x:c r="V4" s="12"/>
       <x:c r="W4" s="9"/>
       <x:c r="X4" s="13"/>
+      <x:c r="Y4"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="10"/>
@@ -684,6 +694,7 @@
       <x:c r="V5" s="12"/>
       <x:c r="W5" s="9"/>
       <x:c r="X5" s="13"/>
+      <x:c r="Y5"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="10"/>
@@ -710,6 +721,7 @@
       <x:c r="V6" s="12"/>
       <x:c r="W6" s="9"/>
       <x:c r="X6" s="13"/>
+      <x:c r="Y6"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="10"/>
@@ -736,6 +748,7 @@
       <x:c r="V7" s="12"/>
       <x:c r="W7" s="9"/>
       <x:c r="X7" s="13"/>
+      <x:c r="Y7"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="10"/>
@@ -762,6 +775,7 @@
       <x:c r="V8" s="12"/>
       <x:c r="W8" s="9"/>
       <x:c r="X8" s="13"/>
+      <x:c r="Y8"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="10"/>
@@ -788,6 +802,7 @@
       <x:c r="V9" s="12"/>
       <x:c r="W9" s="9"/>
       <x:c r="X9" s="13"/>
+      <x:c r="Y9"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="10"/>
@@ -814,6 +829,7 @@
       <x:c r="V10" s="12"/>
       <x:c r="W10" s="9"/>
       <x:c r="X10" s="13"/>
+      <x:c r="Y10"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="10"/>
@@ -840,6 +856,7 @@
       <x:c r="V11" s="12"/>
       <x:c r="W11" s="9"/>
       <x:c r="X11" s="13"/>
+      <x:c r="Y11"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="10"/>
@@ -866,6 +883,7 @@
       <x:c r="V12" s="12"/>
       <x:c r="W12" s="9"/>
       <x:c r="X12" s="13"/>
+      <x:c r="Y12"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="10"/>
@@ -892,6 +910,7 @@
       <x:c r="V13" s="12"/>
       <x:c r="W13" s="9"/>
       <x:c r="X13" s="13"/>
+      <x:c r="Y13"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="10"/>
@@ -918,6 +937,7 @@
       <x:c r="V14" s="12"/>
       <x:c r="W14" s="9"/>
       <x:c r="X14" s="13"/>
+      <x:c r="Y14"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="10"/>
@@ -944,6 +964,7 @@
       <x:c r="V15" s="12"/>
       <x:c r="W15" s="9"/>
       <x:c r="X15" s="13"/>
+      <x:c r="Y15"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="10"/>
@@ -970,6 +991,7 @@
       <x:c r="V16" s="12"/>
       <x:c r="W16" s="9"/>
       <x:c r="X16" s="13"/>
+      <x:c r="Y16"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="10"/>
@@ -996,6 +1018,7 @@
       <x:c r="V17" s="12"/>
       <x:c r="W17" s="9"/>
       <x:c r="X17" s="13"/>
+      <x:c r="Y17"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="10"/>
@@ -1022,6 +1045,7 @@
       <x:c r="V18" s="12"/>
       <x:c r="W18" s="9"/>
       <x:c r="X18" s="13"/>
+      <x:c r="Y18"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="10"/>
@@ -1048,6 +1072,7 @@
       <x:c r="V19" s="12"/>
       <x:c r="W19" s="9"/>
       <x:c r="X19" s="13"/>
+      <x:c r="Y19"/>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="10"/>
@@ -1074,6 +1099,7 @@
       <x:c r="V20" s="12"/>
       <x:c r="W20" s="9"/>
       <x:c r="X20" s="13"/>
+      <x:c r="Y20"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="10"/>
@@ -1100,6 +1126,7 @@
       <x:c r="V21" s="12"/>
       <x:c r="W21" s="9"/>
       <x:c r="X21" s="13"/>
+      <x:c r="Y21"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="10"/>
@@ -1126,6 +1153,7 @@
       <x:c r="V22" s="12"/>
       <x:c r="W22" s="9"/>
       <x:c r="X22" s="13"/>
+      <x:c r="Y22"/>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="10"/>
@@ -1152,6 +1180,7 @@
       <x:c r="V23" s="12"/>
       <x:c r="W23" s="9"/>
       <x:c r="X23" s="13"/>
+      <x:c r="Y23"/>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="10"/>
@@ -1178,6 +1207,7 @@
       <x:c r="V24" s="12"/>
       <x:c r="W24" s="9"/>
       <x:c r="X24" s="13"/>
+      <x:c r="Y24"/>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="10"/>
@@ -1204,6 +1234,7 @@
       <x:c r="V25" s="12"/>
       <x:c r="W25" s="9"/>
       <x:c r="X25" s="13"/>
+      <x:c r="Y25"/>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="10"/>
@@ -1230,6 +1261,7 @@
       <x:c r="V26" s="12"/>
       <x:c r="W26" s="9"/>
       <x:c r="X26" s="13"/>
+      <x:c r="Y26"/>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="10"/>
@@ -1256,6 +1288,7 @@
       <x:c r="V27" s="12"/>
       <x:c r="W27" s="9"/>
       <x:c r="X27" s="13"/>
+      <x:c r="Y27"/>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="10"/>
@@ -1282,6 +1315,7 @@
       <x:c r="V28" s="12"/>
       <x:c r="W28" s="9"/>
       <x:c r="X28" s="13"/>
+      <x:c r="Y28"/>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="10"/>
@@ -1308,6 +1342,7 @@
       <x:c r="V29" s="12"/>
       <x:c r="W29" s="9"/>
       <x:c r="X29" s="13"/>
+      <x:c r="Y29"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="10"/>
@@ -1334,6 +1369,7 @@
       <x:c r="V30" s="12"/>
       <x:c r="W30" s="9"/>
       <x:c r="X30" s="13"/>
+      <x:c r="Y30"/>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="10"/>
@@ -1360,6 +1396,7 @@
       <x:c r="V31" s="12"/>
       <x:c r="W31" s="9"/>
       <x:c r="X31" s="13"/>
+      <x:c r="Y31"/>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="10"/>
@@ -1386,6 +1423,7 @@
       <x:c r="V32" s="12"/>
       <x:c r="W32" s="9"/>
       <x:c r="X32" s="13"/>
+      <x:c r="Y32"/>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="10"/>
@@ -1412,6 +1450,7 @@
       <x:c r="V33" s="12"/>
       <x:c r="W33" s="9"/>
       <x:c r="X33" s="13"/>
+      <x:c r="Y33"/>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="10"/>
@@ -1438,6 +1477,7 @@
       <x:c r="V34" s="12"/>
       <x:c r="W34" s="9"/>
       <x:c r="X34" s="13"/>
+      <x:c r="Y34"/>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="10"/>
@@ -1464,6 +1504,7 @@
       <x:c r="V35" s="12"/>
       <x:c r="W35" s="9"/>
       <x:c r="X35" s="13"/>
+      <x:c r="Y35"/>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="10"/>
@@ -1490,6 +1531,7 @@
       <x:c r="V36" s="12"/>
       <x:c r="W36" s="9"/>
       <x:c r="X36" s="13"/>
+      <x:c r="Y36"/>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="10"/>
@@ -1516,6 +1558,7 @@
       <x:c r="V37" s="12"/>
       <x:c r="W37" s="9"/>
       <x:c r="X37" s="13"/>
+      <x:c r="Y37"/>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="10"/>
@@ -1542,6 +1585,7 @@
       <x:c r="V38" s="12"/>
       <x:c r="W38" s="9"/>
       <x:c r="X38" s="13"/>
+      <x:c r="Y38"/>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="10"/>
@@ -1568,6 +1612,7 @@
       <x:c r="V39" s="12"/>
       <x:c r="W39" s="9"/>
       <x:c r="X39" s="13"/>
+      <x:c r="Y39"/>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="10"/>
@@ -1594,6 +1639,7 @@
       <x:c r="V40" s="12"/>
       <x:c r="W40" s="9"/>
       <x:c r="X40" s="13"/>
+      <x:c r="Y40"/>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="10"/>
@@ -1620,6 +1666,7 @@
       <x:c r="V41" s="12"/>
       <x:c r="W41" s="9"/>
       <x:c r="X41" s="13"/>
+      <x:c r="Y41"/>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="10"/>
@@ -1646,6 +1693,7 @@
       <x:c r="V42" s="12"/>
       <x:c r="W42" s="9"/>
       <x:c r="X42" s="13"/>
+      <x:c r="Y42"/>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="10"/>
@@ -1672,6 +1720,7 @@
       <x:c r="V43" s="12"/>
       <x:c r="W43" s="9"/>
       <x:c r="X43" s="13"/>
+      <x:c r="Y43"/>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="10"/>
@@ -1698,6 +1747,7 @@
       <x:c r="V44" s="12"/>
       <x:c r="W44" s="9"/>
       <x:c r="X44" s="13"/>
+      <x:c r="Y44"/>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="10"/>
@@ -1724,6 +1774,7 @@
       <x:c r="V45" s="12"/>
       <x:c r="W45" s="9"/>
       <x:c r="X45" s="13"/>
+      <x:c r="Y45"/>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="10"/>
@@ -1750,6 +1801,7 @@
       <x:c r="V46" s="12"/>
       <x:c r="W46" s="9"/>
       <x:c r="X46" s="13"/>
+      <x:c r="Y46"/>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="10"/>
@@ -1776,6 +1828,7 @@
       <x:c r="V47" s="12"/>
       <x:c r="W47" s="9"/>
       <x:c r="X47" s="13"/>
+      <x:c r="Y47"/>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="10"/>
@@ -1802,6 +1855,7 @@
       <x:c r="V48" s="12"/>
       <x:c r="W48" s="9"/>
       <x:c r="X48" s="13"/>
+      <x:c r="Y48"/>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="10"/>
@@ -1828,6 +1882,7 @@
       <x:c r="V49" s="12"/>
       <x:c r="W49" s="9"/>
       <x:c r="X49" s="13"/>
+      <x:c r="Y49"/>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="10"/>
@@ -1854,6 +1909,7 @@
       <x:c r="V50" s="12"/>
       <x:c r="W50" s="9"/>
       <x:c r="X50" s="13"/>
+      <x:c r="Y50"/>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="10"/>
@@ -1880,6 +1936,7 @@
       <x:c r="V51" s="12"/>
       <x:c r="W51" s="9"/>
       <x:c r="X51" s="13"/>
+      <x:c r="Y51"/>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="10"/>
@@ -1906,6 +1963,7 @@
       <x:c r="V52" s="12"/>
       <x:c r="W52" s="9"/>
       <x:c r="X52" s="13"/>
+      <x:c r="Y52"/>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="10"/>
@@ -1932,6 +1990,7 @@
       <x:c r="V53" s="12"/>
       <x:c r="W53" s="9"/>
       <x:c r="X53" s="13"/>
+      <x:c r="Y53"/>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="10"/>
@@ -1958,6 +2017,7 @@
       <x:c r="V54" s="12"/>
       <x:c r="W54" s="9"/>
       <x:c r="X54" s="13"/>
+      <x:c r="Y54"/>
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="10"/>
@@ -1984,6 +2044,7 @@
       <x:c r="V55" s="12"/>
       <x:c r="W55" s="9"/>
       <x:c r="X55" s="13"/>
+      <x:c r="Y55"/>
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="10"/>
@@ -2010,6 +2071,7 @@
       <x:c r="V56" s="12"/>
       <x:c r="W56" s="9"/>
       <x:c r="X56" s="13"/>
+      <x:c r="Y56"/>
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="10"/>
@@ -2036,6 +2098,7 @@
       <x:c r="V57" s="12"/>
       <x:c r="W57" s="9"/>
       <x:c r="X57" s="13"/>
+      <x:c r="Y57"/>
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="10"/>
@@ -2062,6 +2125,7 @@
       <x:c r="V58" s="12"/>
       <x:c r="W58" s="9"/>
       <x:c r="X58" s="13"/>
+      <x:c r="Y58"/>
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="10"/>
@@ -2088,6 +2152,7 @@
       <x:c r="V59" s="12"/>
       <x:c r="W59" s="9"/>
       <x:c r="X59" s="13"/>
+      <x:c r="Y59"/>
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="10"/>
@@ -2114,6 +2179,7 @@
       <x:c r="V60" s="12"/>
       <x:c r="W60" s="9"/>
       <x:c r="X60" s="13"/>
+      <x:c r="Y60"/>
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="10"/>
@@ -2140,6 +2206,7 @@
       <x:c r="V61" s="12"/>
       <x:c r="W61" s="9"/>
       <x:c r="X61" s="13"/>
+      <x:c r="Y61"/>
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="10"/>
@@ -2166,6 +2233,7 @@
       <x:c r="V62" s="12"/>
       <x:c r="W62" s="9"/>
       <x:c r="X62" s="13"/>
+      <x:c r="Y62"/>
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="10"/>
@@ -2192,6 +2260,7 @@
       <x:c r="V63" s="12"/>
       <x:c r="W63" s="9"/>
       <x:c r="X63" s="13"/>
+      <x:c r="Y63"/>
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="10"/>
@@ -2218,6 +2287,7 @@
       <x:c r="V64" s="12"/>
       <x:c r="W64" s="9"/>
       <x:c r="X64" s="13"/>
+      <x:c r="Y64"/>
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="10"/>
@@ -2244,6 +2314,7 @@
       <x:c r="V65" s="12"/>
       <x:c r="W65" s="9"/>
       <x:c r="X65" s="13"/>
+      <x:c r="Y65"/>
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="10"/>
@@ -2270,6 +2341,7 @@
       <x:c r="V66" s="12"/>
       <x:c r="W66" s="9"/>
       <x:c r="X66" s="13"/>
+      <x:c r="Y66"/>
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="10"/>
@@ -2296,6 +2368,7 @@
       <x:c r="V67" s="12"/>
       <x:c r="W67" s="9"/>
       <x:c r="X67" s="13"/>
+      <x:c r="Y67"/>
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="10"/>
@@ -2322,6 +2395,7 @@
       <x:c r="V68" s="12"/>
       <x:c r="W68" s="9"/>
       <x:c r="X68" s="13"/>
+      <x:c r="Y68"/>
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="10"/>
@@ -2348,6 +2422,7 @@
       <x:c r="V69" s="12"/>
       <x:c r="W69" s="9"/>
       <x:c r="X69" s="13"/>
+      <x:c r="Y69"/>
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="10"/>
@@ -2374,6 +2449,7 @@
       <x:c r="V70" s="12"/>
       <x:c r="W70" s="9"/>
       <x:c r="X70" s="13"/>
+      <x:c r="Y70"/>
     </x:row>
     <x:row r="71">
       <x:c r="A71" s="10"/>
@@ -2400,6 +2476,7 @@
       <x:c r="V71" s="12"/>
       <x:c r="W71" s="9"/>
       <x:c r="X71" s="13"/>
+      <x:c r="Y71"/>
     </x:row>
     <x:row r="72">
       <x:c r="A72" s="10"/>
@@ -2426,6 +2503,7 @@
       <x:c r="V72" s="12"/>
       <x:c r="W72" s="9"/>
       <x:c r="X72" s="13"/>
+      <x:c r="Y72"/>
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="10"/>
@@ -2452,6 +2530,7 @@
       <x:c r="V73" s="12"/>
       <x:c r="W73" s="9"/>
       <x:c r="X73" s="13"/>
+      <x:c r="Y73"/>
     </x:row>
     <x:row r="74">
       <x:c r="A74" s="10"/>
@@ -2478,6 +2557,7 @@
       <x:c r="V74" s="12"/>
       <x:c r="W74" s="9"/>
       <x:c r="X74" s="13"/>
+      <x:c r="Y74"/>
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="10"/>
@@ -2504,6 +2584,7 @@
       <x:c r="V75" s="12"/>
       <x:c r="W75" s="9"/>
       <x:c r="X75" s="13"/>
+      <x:c r="Y75"/>
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="10"/>
@@ -2530,6 +2611,7 @@
       <x:c r="V76" s="12"/>
       <x:c r="W76" s="9"/>
       <x:c r="X76" s="13"/>
+      <x:c r="Y76"/>
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="10"/>
@@ -2556,6 +2638,7 @@
       <x:c r="V77" s="12"/>
       <x:c r="W77" s="9"/>
       <x:c r="X77" s="13"/>
+      <x:c r="Y77"/>
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="10"/>
@@ -2582,6 +2665,7 @@
       <x:c r="V78" s="12"/>
       <x:c r="W78" s="9"/>
       <x:c r="X78" s="13"/>
+      <x:c r="Y78"/>
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="10"/>
@@ -2608,6 +2692,7 @@
       <x:c r="V79" s="12"/>
       <x:c r="W79" s="9"/>
       <x:c r="X79" s="13"/>
+      <x:c r="Y79"/>
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="10"/>
@@ -2634,6 +2719,7 @@
       <x:c r="V80" s="12"/>
       <x:c r="W80" s="9"/>
       <x:c r="X80" s="13"/>
+      <x:c r="Y80"/>
     </x:row>
     <x:row r="81">
       <x:c r="A81" s="10"/>
@@ -2660,6 +2746,7 @@
       <x:c r="V81" s="12"/>
       <x:c r="W81" s="9"/>
       <x:c r="X81" s="13"/>
+      <x:c r="Y81"/>
     </x:row>
     <x:row r="82">
       <x:c r="A82" s="10"/>
@@ -2686,6 +2773,7 @@
       <x:c r="V82" s="12"/>
       <x:c r="W82" s="9"/>
       <x:c r="X82" s="13"/>
+      <x:c r="Y82"/>
     </x:row>
     <x:row r="83">
       <x:c r="A83" s="10"/>
@@ -2712,6 +2800,7 @@
       <x:c r="V83" s="12"/>
       <x:c r="W83" s="9"/>
       <x:c r="X83" s="13"/>
+      <x:c r="Y83"/>
     </x:row>
     <x:row r="84">
       <x:c r="A84" s="10"/>
@@ -2738,6 +2827,7 @@
       <x:c r="V84" s="12"/>
       <x:c r="W84" s="9"/>
       <x:c r="X84" s="13"/>
+      <x:c r="Y84"/>
     </x:row>
     <x:row r="85">
       <x:c r="A85" s="10"/>
@@ -2764,6 +2854,7 @@
       <x:c r="V85" s="12"/>
       <x:c r="W85" s="9"/>
       <x:c r="X85" s="13"/>
+      <x:c r="Y85"/>
     </x:row>
     <x:row r="86">
       <x:c r="A86" s="10"/>
@@ -2790,6 +2881,7 @@
       <x:c r="V86" s="12"/>
       <x:c r="W86" s="9"/>
       <x:c r="X86" s="13"/>
+      <x:c r="Y86"/>
     </x:row>
     <x:row r="87">
       <x:c r="A87" s="10"/>
@@ -2816,6 +2908,7 @@
       <x:c r="V87" s="12"/>
       <x:c r="W87" s="9"/>
       <x:c r="X87" s="13"/>
+      <x:c r="Y87"/>
     </x:row>
     <x:row r="88">
       <x:c r="A88" s="10"/>
@@ -2842,6 +2935,7 @@
       <x:c r="V88" s="12"/>
       <x:c r="W88" s="9"/>
       <x:c r="X88" s="13"/>
+      <x:c r="Y88"/>
     </x:row>
     <x:row r="89">
       <x:c r="A89" s="10"/>
@@ -2868,6 +2962,7 @@
       <x:c r="V89" s="12"/>
       <x:c r="W89" s="9"/>
       <x:c r="X89" s="13"/>
+      <x:c r="Y89"/>
     </x:row>
     <x:row r="90">
       <x:c r="A90" s="10"/>
@@ -2894,6 +2989,7 @@
       <x:c r="V90" s="12"/>
       <x:c r="W90" s="9"/>
       <x:c r="X90" s="13"/>
+      <x:c r="Y90"/>
     </x:row>
     <x:row r="91">
       <x:c r="A91" s="10"/>
@@ -2920,6 +3016,7 @@
       <x:c r="V91" s="12"/>
       <x:c r="W91" s="9"/>
       <x:c r="X91" s="13"/>
+      <x:c r="Y91"/>
     </x:row>
     <x:row r="92">
       <x:c r="A92" s="10"/>
@@ -2946,6 +3043,7 @@
       <x:c r="V92" s="12"/>
       <x:c r="W92" s="9"/>
       <x:c r="X92" s="13"/>
+      <x:c r="Y92"/>
     </x:row>
     <x:row r="93">
       <x:c r="A93" s="10"/>
@@ -2972,6 +3070,7 @@
       <x:c r="V93" s="12"/>
       <x:c r="W93" s="9"/>
       <x:c r="X93" s="13"/>
+      <x:c r="Y93"/>
     </x:row>
     <x:row r="94">
       <x:c r="A94" s="10"/>
@@ -2998,6 +3097,7 @@
       <x:c r="V94" s="12"/>
       <x:c r="W94" s="9"/>
       <x:c r="X94" s="13"/>
+      <x:c r="Y94"/>
     </x:row>
     <x:row r="95">
       <x:c r="A95" s="10"/>
@@ -3024,6 +3124,7 @@
       <x:c r="V95" s="12"/>
       <x:c r="W95" s="9"/>
       <x:c r="X95" s="13"/>
+      <x:c r="Y95"/>
     </x:row>
     <x:row r="96">
       <x:c r="A96" s="10"/>
@@ -3050,6 +3151,7 @@
       <x:c r="V96" s="12"/>
       <x:c r="W96" s="9"/>
       <x:c r="X96" s="13"/>
+      <x:c r="Y96"/>
     </x:row>
     <x:row r="97">
       <x:c r="A97" s="10"/>
@@ -3076,6 +3178,7 @@
       <x:c r="V97" s="12"/>
       <x:c r="W97" s="9"/>
       <x:c r="X97" s="13"/>
+      <x:c r="Y97"/>
     </x:row>
     <x:row r="98">
       <x:c r="A98" s="10"/>
@@ -3102,6 +3205,7 @@
       <x:c r="V98" s="12"/>
       <x:c r="W98" s="9"/>
       <x:c r="X98" s="13"/>
+      <x:c r="Y98"/>
     </x:row>
     <x:row r="99">
       <x:c r="A99" s="10"/>
@@ -3128,6 +3232,7 @@
       <x:c r="V99" s="12"/>
       <x:c r="W99" s="9"/>
       <x:c r="X99" s="13"/>
+      <x:c r="Y99"/>
     </x:row>
     <x:row r="100">
       <x:c r="A100" s="10"/>
@@ -3154,6 +3259,7 @@
       <x:c r="V100" s="12"/>
       <x:c r="W100" s="9"/>
       <x:c r="X100" s="13"/>
+      <x:c r="Y100"/>
     </x:row>
     <x:row r="101">
       <x:c r="A101" s="10"/>
@@ -3180,6 +3286,7 @@
       <x:c r="V101" s="12"/>
       <x:c r="W101" s="9"/>
       <x:c r="X101" s="13"/>
+      <x:c r="Y101"/>
     </x:row>
     <x:row r="102">
       <x:c r="A102" s="10"/>
@@ -3206,6 +3313,7 @@
       <x:c r="V102" s="12"/>
       <x:c r="W102" s="9"/>
       <x:c r="X102" s="13"/>
+      <x:c r="Y102"/>
     </x:row>
     <x:row r="103">
       <x:c r="A103" s="10"/>
@@ -3232,6 +3340,7 @@
       <x:c r="V103" s="12"/>
       <x:c r="W103" s="9"/>
       <x:c r="X103" s="13"/>
+      <x:c r="Y103"/>
     </x:row>
     <x:row r="104">
       <x:c r="A104" s="10"/>
@@ -3258,6 +3367,7 @@
       <x:c r="V104" s="12"/>
       <x:c r="W104" s="9"/>
       <x:c r="X104" s="13"/>
+      <x:c r="Y104"/>
     </x:row>
     <x:row r="105">
       <x:c r="A105" s="10"/>
@@ -3284,6 +3394,7 @@
       <x:c r="V105" s="12"/>
       <x:c r="W105" s="9"/>
       <x:c r="X105" s="13"/>
+      <x:c r="Y105"/>
     </x:row>
     <x:row r="106">
       <x:c r="A106" s="10"/>
@@ -3310,6 +3421,7 @@
       <x:c r="V106" s="12"/>
       <x:c r="W106" s="9"/>
       <x:c r="X106" s="13"/>
+      <x:c r="Y106"/>
     </x:row>
     <x:row r="107">
       <x:c r="A107" s="10"/>
@@ -3336,6 +3448,7 @@
       <x:c r="V107" s="12"/>
       <x:c r="W107" s="9"/>
       <x:c r="X107" s="13"/>
+      <x:c r="Y107"/>
     </x:row>
     <x:row r="108">
       <x:c r="A108" s="10"/>
@@ -3362,6 +3475,7 @@
       <x:c r="V108" s="12"/>
       <x:c r="W108" s="9"/>
       <x:c r="X108" s="13"/>
+      <x:c r="Y108"/>
     </x:row>
     <x:row r="109">
       <x:c r="A109" s="10"/>
@@ -3388,6 +3502,7 @@
       <x:c r="V109" s="12"/>
       <x:c r="W109" s="9"/>
       <x:c r="X109" s="13"/>
+      <x:c r="Y109"/>
     </x:row>
     <x:row r="110">
       <x:c r="A110" s="10"/>
@@ -3414,6 +3529,7 @@
       <x:c r="V110" s="12"/>
       <x:c r="W110" s="9"/>
       <x:c r="X110" s="13"/>
+      <x:c r="Y110"/>
     </x:row>
     <x:row r="111">
       <x:c r="A111" s="10"/>
@@ -3440,6 +3556,7 @@
       <x:c r="V111" s="12"/>
       <x:c r="W111" s="9"/>
       <x:c r="X111" s="13"/>
+      <x:c r="Y111"/>
     </x:row>
     <x:row r="112">
       <x:c r="A112" s="10"/>
@@ -3466,6 +3583,7 @@
       <x:c r="V112" s="12"/>
       <x:c r="W112" s="9"/>
       <x:c r="X112" s="13"/>
+      <x:c r="Y112"/>
     </x:row>
     <x:row r="113">
       <x:c r="A113" s="10"/>
@@ -3492,6 +3610,7 @@
       <x:c r="V113" s="12"/>
       <x:c r="W113" s="9"/>
       <x:c r="X113" s="13"/>
+      <x:c r="Y113"/>
     </x:row>
     <x:row r="114">
       <x:c r="A114" s="10"/>
@@ -3518,6 +3637,7 @@
       <x:c r="V114" s="12"/>
       <x:c r="W114" s="9"/>
       <x:c r="X114" s="13"/>
+      <x:c r="Y114"/>
     </x:row>
     <x:row r="115">
       <x:c r="A115" s="10"/>
@@ -3544,6 +3664,7 @@
       <x:c r="V115" s="12"/>
       <x:c r="W115" s="9"/>
       <x:c r="X115" s="13"/>
+      <x:c r="Y115"/>
     </x:row>
     <x:row r="116">
       <x:c r="A116" s="10"/>
@@ -3570,6 +3691,7 @@
       <x:c r="V116" s="12"/>
       <x:c r="W116" s="9"/>
       <x:c r="X116" s="13"/>
+      <x:c r="Y116"/>
     </x:row>
     <x:row r="117">
       <x:c r="A117" s="10"/>
@@ -3596,6 +3718,7 @@
       <x:c r="V117" s="12"/>
       <x:c r="W117" s="9"/>
       <x:c r="X117" s="13"/>
+      <x:c r="Y117"/>
     </x:row>
     <x:row r="118">
       <x:c r="A118" s="10"/>
@@ -3622,6 +3745,7 @@
       <x:c r="V118" s="12"/>
       <x:c r="W118" s="9"/>
       <x:c r="X118" s="13"/>
+      <x:c r="Y118"/>
     </x:row>
     <x:row r="119">
       <x:c r="A119" s="10"/>
@@ -3648,6 +3772,7 @@
       <x:c r="V119" s="12"/>
       <x:c r="W119" s="9"/>
       <x:c r="X119" s="13"/>
+      <x:c r="Y119"/>
     </x:row>
     <x:row r="120">
       <x:c r="A120" s="10"/>
@@ -3674,6 +3799,7 @@
       <x:c r="V120" s="12"/>
       <x:c r="W120" s="9"/>
       <x:c r="X120" s="13"/>
+      <x:c r="Y120"/>
     </x:row>
     <x:row r="121">
       <x:c r="A121" s="10"/>
@@ -3700,6 +3826,7 @@
       <x:c r="V121" s="12"/>
       <x:c r="W121" s="9"/>
       <x:c r="X121" s="13"/>
+      <x:c r="Y121"/>
     </x:row>
     <x:row r="122">
       <x:c r="A122" s="10"/>
@@ -3726,6 +3853,7 @@
       <x:c r="V122" s="12"/>
       <x:c r="W122" s="9"/>
       <x:c r="X122" s="13"/>
+      <x:c r="Y122"/>
     </x:row>
     <x:row r="123">
       <x:c r="A123" s="10"/>
@@ -3752,6 +3880,7 @@
       <x:c r="V123" s="12"/>
       <x:c r="W123" s="9"/>
       <x:c r="X123" s="13"/>
+      <x:c r="Y123"/>
     </x:row>
     <x:row r="124">
       <x:c r="A124" s="10"/>
@@ -3778,6 +3907,7 @@
       <x:c r="V124" s="12"/>
       <x:c r="W124" s="9"/>
       <x:c r="X124" s="13"/>
+      <x:c r="Y124"/>
     </x:row>
     <x:row r="125">
       <x:c r="A125" s="10"/>
@@ -3804,6 +3934,7 @@
       <x:c r="V125" s="12"/>
       <x:c r="W125" s="9"/>
       <x:c r="X125" s="13"/>
+      <x:c r="Y125"/>
     </x:row>
     <x:row r="126">
       <x:c r="A126" s="10"/>
@@ -3830,6 +3961,7 @@
       <x:c r="V126" s="12"/>
       <x:c r="W126" s="9"/>
       <x:c r="X126" s="13"/>
+      <x:c r="Y126"/>
     </x:row>
     <x:row r="127">
       <x:c r="A127" s="10"/>
@@ -3856,6 +3988,7 @@
       <x:c r="V127" s="12"/>
       <x:c r="W127" s="9"/>
       <x:c r="X127" s="13"/>
+      <x:c r="Y127"/>
     </x:row>
     <x:row r="128">
       <x:c r="A128" s="10"/>
@@ -3882,6 +4015,7 @@
       <x:c r="V128" s="12"/>
       <x:c r="W128" s="9"/>
       <x:c r="X128" s="13"/>
+      <x:c r="Y128"/>
     </x:row>
     <x:row r="129">
       <x:c r="A129" s="10"/>
@@ -3908,6 +4042,7 @@
       <x:c r="V129" s="12"/>
       <x:c r="W129" s="9"/>
       <x:c r="X129" s="13"/>
+      <x:c r="Y129"/>
     </x:row>
     <x:row r="130">
       <x:c r="A130" s="10"/>
@@ -3934,6 +4069,7 @@
       <x:c r="V130" s="12"/>
       <x:c r="W130" s="9"/>
       <x:c r="X130" s="13"/>
+      <x:c r="Y130"/>
     </x:row>
     <x:row r="131">
       <x:c r="A131" s="10"/>
@@ -3960,6 +4096,7 @@
       <x:c r="V131" s="12"/>
       <x:c r="W131" s="9"/>
       <x:c r="X131" s="13"/>
+      <x:c r="Y131"/>
     </x:row>
     <x:row r="132">
       <x:c r="A132" s="10"/>
@@ -3986,6 +4123,7 @@
       <x:c r="V132" s="12"/>
       <x:c r="W132" s="9"/>
       <x:c r="X132" s="13"/>
+      <x:c r="Y132"/>
     </x:row>
     <x:row r="133">
       <x:c r="A133" s="10"/>
@@ -4012,6 +4150,7 @@
       <x:c r="V133" s="12"/>
       <x:c r="W133" s="9"/>
       <x:c r="X133" s="13"/>
+      <x:c r="Y133"/>
     </x:row>
     <x:row r="134">
       <x:c r="A134" s="10"/>
@@ -4038,6 +4177,7 @@
       <x:c r="V134" s="12"/>
       <x:c r="W134" s="9"/>
       <x:c r="X134" s="13"/>
+      <x:c r="Y134"/>
     </x:row>
     <x:row r="135">
       <x:c r="A135" s="10"/>
@@ -4064,6 +4204,7 @@
       <x:c r="V135" s="12"/>
       <x:c r="W135" s="9"/>
       <x:c r="X135" s="13"/>
+      <x:c r="Y135"/>
     </x:row>
     <x:row r="136">
       <x:c r="A136" s="10"/>
@@ -4090,6 +4231,7 @@
       <x:c r="V136" s="12"/>
       <x:c r="W136" s="9"/>
       <x:c r="X136" s="13"/>
+      <x:c r="Y136"/>
     </x:row>
     <x:row r="137">
       <x:c r="A137" s="10"/>
@@ -4116,6 +4258,7 @@
       <x:c r="V137" s="12"/>
       <x:c r="W137" s="9"/>
       <x:c r="X137" s="13"/>
+      <x:c r="Y137"/>
     </x:row>
     <x:row r="138">
       <x:c r="A138" s="10"/>
@@ -4142,6 +4285,7 @@
       <x:c r="V138" s="12"/>
       <x:c r="W138" s="9"/>
       <x:c r="X138" s="13"/>
+      <x:c r="Y138"/>
     </x:row>
     <x:row r="139">
       <x:c r="A139" s="10"/>
@@ -4168,6 +4312,7 @@
       <x:c r="V139" s="12"/>
       <x:c r="W139" s="9"/>
       <x:c r="X139" s="13"/>
+      <x:c r="Y139"/>
     </x:row>
     <x:row r="140">
       <x:c r="A140" s="10"/>
@@ -4194,6 +4339,7 @@
       <x:c r="V140" s="12"/>
       <x:c r="W140" s="9"/>
       <x:c r="X140" s="13"/>
+      <x:c r="Y140"/>
     </x:row>
     <x:row r="141">
       <x:c r="A141" s="10"/>
@@ -4220,6 +4366,7 @@
       <x:c r="V141" s="12"/>
       <x:c r="W141" s="9"/>
       <x:c r="X141" s="13"/>
+      <x:c r="Y141"/>
     </x:row>
     <x:row r="142">
       <x:c r="A142" s="10"/>
@@ -4246,6 +4393,7 @@
       <x:c r="V142" s="12"/>
       <x:c r="W142" s="9"/>
       <x:c r="X142" s="13"/>
+      <x:c r="Y142"/>
     </x:row>
     <x:row r="143">
       <x:c r="A143" s="10"/>
@@ -4272,6 +4420,7 @@
       <x:c r="V143" s="12"/>
       <x:c r="W143" s="9"/>
       <x:c r="X143" s="13"/>
+      <x:c r="Y143"/>
     </x:row>
     <x:row r="144">
       <x:c r="A144" s="10"/>
@@ -4298,6 +4447,7 @@
       <x:c r="V144" s="12"/>
       <x:c r="W144" s="9"/>
       <x:c r="X144" s="13"/>
+      <x:c r="Y144"/>
     </x:row>
     <x:row r="145">
       <x:c r="A145" s="10"/>
@@ -4324,6 +4474,7 @@
       <x:c r="V145" s="12"/>
       <x:c r="W145" s="9"/>
       <x:c r="X145" s="13"/>
+      <x:c r="Y145"/>
     </x:row>
     <x:row r="146">
       <x:c r="A146" s="10"/>
@@ -4350,6 +4501,7 @@
       <x:c r="V146" s="12"/>
       <x:c r="W146" s="9"/>
       <x:c r="X146" s="13"/>
+      <x:c r="Y146"/>
     </x:row>
     <x:row r="147">
       <x:c r="A147" s="10"/>
@@ -4376,6 +4528,7 @@
       <x:c r="V147" s="12"/>
       <x:c r="W147" s="9"/>
       <x:c r="X147" s="13"/>
+      <x:c r="Y147"/>
     </x:row>
     <x:row r="148">
       <x:c r="A148" s="10"/>
@@ -4402,6 +4555,7 @@
       <x:c r="V148" s="12"/>
       <x:c r="W148" s="9"/>
       <x:c r="X148" s="13"/>
+      <x:c r="Y148"/>
     </x:row>
     <x:row r="149">
       <x:c r="A149" s="10"/>
@@ -4428,6 +4582,7 @@
       <x:c r="V149" s="12"/>
       <x:c r="W149" s="9"/>
       <x:c r="X149" s="13"/>
+      <x:c r="Y149"/>
     </x:row>
     <x:row r="150">
       <x:c r="A150" s="10"/>
@@ -4454,6 +4609,7 @@
       <x:c r="V150" s="12"/>
       <x:c r="W150" s="9"/>
       <x:c r="X150" s="13"/>
+      <x:c r="Y150"/>
     </x:row>
     <x:row r="151">
       <x:c r="A151" s="10"/>
@@ -4480,6 +4636,7 @@
       <x:c r="V151" s="12"/>
       <x:c r="W151" s="9"/>
       <x:c r="X151" s="13"/>
+      <x:c r="Y151"/>
     </x:row>
     <x:row r="152">
       <x:c r="A152" s="10"/>
@@ -4506,6 +4663,7 @@
       <x:c r="V152" s="12"/>
       <x:c r="W152" s="9"/>
       <x:c r="X152" s="13"/>
+      <x:c r="Y152"/>
     </x:row>
     <x:row r="153">
       <x:c r="A153" s="10"/>
@@ -4532,6 +4690,7 @@
       <x:c r="V153" s="12"/>
       <x:c r="W153" s="9"/>
       <x:c r="X153" s="13"/>
+      <x:c r="Y153"/>
     </x:row>
     <x:row r="154">
       <x:c r="A154" s="10"/>
@@ -4558,6 +4717,7 @@
       <x:c r="V154" s="12"/>
       <x:c r="W154" s="9"/>
       <x:c r="X154" s="13"/>
+      <x:c r="Y154"/>
     </x:row>
     <x:row r="155">
       <x:c r="A155" s="10"/>
@@ -4584,6 +4744,7 @@
       <x:c r="V155" s="12"/>
       <x:c r="W155" s="9"/>
       <x:c r="X155" s="13"/>
+      <x:c r="Y155"/>
     </x:row>
     <x:row r="156">
       <x:c r="A156" s="10"/>
@@ -4610,6 +4771,7 @@
       <x:c r="V156" s="12"/>
       <x:c r="W156" s="9"/>
       <x:c r="X156" s="13"/>
+      <x:c r="Y156"/>
     </x:row>
     <x:row r="157">
       <x:c r="A157" s="10"/>
@@ -4636,6 +4798,7 @@
       <x:c r="V157" s="12"/>
       <x:c r="W157" s="9"/>
       <x:c r="X157" s="13"/>
+      <x:c r="Y157"/>
     </x:row>
     <x:row r="158">
       <x:c r="A158" s="10"/>
@@ -4662,6 +4825,7 @@
       <x:c r="V158" s="12"/>
       <x:c r="W158" s="9"/>
       <x:c r="X158" s="13"/>
+      <x:c r="Y158"/>
     </x:row>
     <x:row r="159">
       <x:c r="A159" s="10"/>
@@ -4688,6 +4852,7 @@
       <x:c r="V159" s="12"/>
       <x:c r="W159" s="9"/>
       <x:c r="X159" s="13"/>
+      <x:c r="Y159"/>
     </x:row>
     <x:row r="160">
       <x:c r="A160" s="10"/>
@@ -4714,6 +4879,7 @@
       <x:c r="V160" s="12"/>
       <x:c r="W160" s="9"/>
       <x:c r="X160" s="13"/>
+      <x:c r="Y160"/>
     </x:row>
     <x:row r="161">
       <x:c r="A161" s="10"/>
@@ -4740,6 +4906,7 @@
       <x:c r="V161" s="12"/>
       <x:c r="W161" s="9"/>
       <x:c r="X161" s="13"/>
+      <x:c r="Y161"/>
     </x:row>
     <x:row r="162">
       <x:c r="A162" s="10"/>
@@ -4766,6 +4933,7 @@
       <x:c r="V162" s="12"/>
       <x:c r="W162" s="9"/>
       <x:c r="X162" s="13"/>
+      <x:c r="Y162"/>
     </x:row>
     <x:row r="163">
       <x:c r="A163" s="10"/>
@@ -4792,6 +4960,7 @@
       <x:c r="V163" s="12"/>
       <x:c r="W163" s="9"/>
       <x:c r="X163" s="13"/>
+      <x:c r="Y163"/>
     </x:row>
     <x:row r="164">
       <x:c r="A164" s="10"/>
@@ -4818,6 +4987,7 @@
       <x:c r="V164" s="12"/>
       <x:c r="W164" s="9"/>
       <x:c r="X164" s="13"/>
+      <x:c r="Y164"/>
     </x:row>
     <x:row r="165">
       <x:c r="A165" s="10"/>
@@ -4844,6 +5014,7 @@
       <x:c r="V165" s="12"/>
       <x:c r="W165" s="9"/>
       <x:c r="X165" s="13"/>
+      <x:c r="Y165"/>
     </x:row>
     <x:row r="166">
       <x:c r="A166" s="10"/>
@@ -4870,6 +5041,7 @@
       <x:c r="V166" s="12"/>
       <x:c r="W166" s="9"/>
       <x:c r="X166" s="13"/>
+      <x:c r="Y166"/>
     </x:row>
     <x:row r="167">
       <x:c r="A167" s="10"/>
@@ -4896,6 +5068,7 @@
       <x:c r="V167" s="12"/>
       <x:c r="W167" s="9"/>
       <x:c r="X167" s="13"/>
+      <x:c r="Y167"/>
     </x:row>
     <x:row r="168">
       <x:c r="A168" s="10"/>
@@ -4922,6 +5095,7 @@
       <x:c r="V168" s="12"/>
       <x:c r="W168" s="9"/>
       <x:c r="X168" s="13"/>
+      <x:c r="Y168"/>
     </x:row>
     <x:row r="169">
       <x:c r="A169" s="10"/>
@@ -4948,6 +5122,7 @@
       <x:c r="V169" s="12"/>
       <x:c r="W169" s="9"/>
       <x:c r="X169" s="13"/>
+      <x:c r="Y169"/>
     </x:row>
     <x:row r="170">
       <x:c r="A170" s="10"/>
@@ -4974,6 +5149,7 @@
       <x:c r="V170" s="12"/>
       <x:c r="W170" s="9"/>
       <x:c r="X170" s="13"/>
+      <x:c r="Y170"/>
     </x:row>
     <x:row r="171">
       <x:c r="A171" s="10"/>
@@ -5000,6 +5176,7 @@
       <x:c r="V171" s="12"/>
       <x:c r="W171" s="9"/>
       <x:c r="X171" s="13"/>
+      <x:c r="Y171"/>
     </x:row>
     <x:row r="172">
       <x:c r="A172" s="10"/>
@@ -5026,6 +5203,7 @@
       <x:c r="V172" s="12"/>
       <x:c r="W172" s="9"/>
       <x:c r="X172" s="13"/>
+      <x:c r="Y172"/>
     </x:row>
     <x:row r="173">
       <x:c r="A173" s="10"/>
@@ -5052,6 +5230,7 @@
       <x:c r="V173" s="12"/>
       <x:c r="W173" s="9"/>
       <x:c r="X173" s="13"/>
+      <x:c r="Y173"/>
     </x:row>
     <x:row r="174">
       <x:c r="A174" s="10"/>
@@ -5078,6 +5257,7 @@
       <x:c r="V174" s="12"/>
       <x:c r="W174" s="9"/>
       <x:c r="X174" s="13"/>
+      <x:c r="Y174"/>
     </x:row>
     <x:row r="175">
       <x:c r="A175" s="10"/>
@@ -5104,6 +5284,7 @@
       <x:c r="V175" s="12"/>
       <x:c r="W175" s="9"/>
       <x:c r="X175" s="13"/>
+      <x:c r="Y175"/>
     </x:row>
     <x:row r="176">
       <x:c r="A176" s="10"/>
@@ -5130,6 +5311,7 @@
       <x:c r="V176" s="12"/>
       <x:c r="W176" s="9"/>
       <x:c r="X176" s="13"/>
+      <x:c r="Y176"/>
     </x:row>
     <x:row r="177">
       <x:c r="A177" s="10"/>
@@ -5156,6 +5338,7 @@
       <x:c r="V177" s="12"/>
       <x:c r="W177" s="9"/>
       <x:c r="X177" s="13"/>
+      <x:c r="Y177"/>
     </x:row>
     <x:row r="178">
       <x:c r="A178" s="10"/>
@@ -5182,6 +5365,7 @@
       <x:c r="V178" s="12"/>
       <x:c r="W178" s="9"/>
       <x:c r="X178" s="13"/>
+      <x:c r="Y178"/>
     </x:row>
     <x:row r="179">
       <x:c r="A179" s="10"/>
@@ -5208,6 +5392,7 @@
       <x:c r="V179" s="12"/>
       <x:c r="W179" s="9"/>
       <x:c r="X179" s="13"/>
+      <x:c r="Y179"/>
     </x:row>
     <x:row r="180">
       <x:c r="A180" s="10"/>
@@ -5234,6 +5419,7 @@
       <x:c r="V180" s="12"/>
       <x:c r="W180" s="9"/>
       <x:c r="X180" s="13"/>
+      <x:c r="Y180"/>
     </x:row>
     <x:row r="181">
       <x:c r="A181" s="10"/>
@@ -5260,6 +5446,7 @@
       <x:c r="V181" s="12"/>
       <x:c r="W181" s="9"/>
       <x:c r="X181" s="13"/>
+      <x:c r="Y181"/>
     </x:row>
     <x:row r="182">
       <x:c r="A182" s="10"/>
@@ -5286,6 +5473,7 @@
       <x:c r="V182" s="12"/>
       <x:c r="W182" s="9"/>
       <x:c r="X182" s="13"/>
+      <x:c r="Y182"/>
     </x:row>
     <x:row r="183">
       <x:c r="A183" s="10"/>
@@ -5312,6 +5500,7 @@
       <x:c r="V183" s="12"/>
       <x:c r="W183" s="9"/>
       <x:c r="X183" s="13"/>
+      <x:c r="Y183"/>
     </x:row>
     <x:row r="184">
       <x:c r="A184" s="10"/>
@@ -5338,6 +5527,7 @@
       <x:c r="V184" s="12"/>
       <x:c r="W184" s="9"/>
       <x:c r="X184" s="13"/>
+      <x:c r="Y184"/>
     </x:row>
     <x:row r="185">
       <x:c r="A185" s="10"/>
@@ -5364,6 +5554,7 @@
       <x:c r="V185" s="12"/>
       <x:c r="W185" s="9"/>
       <x:c r="X185" s="13"/>
+      <x:c r="Y185"/>
     </x:row>
     <x:row r="186">
       <x:c r="A186" s="10"/>
@@ -5390,6 +5581,7 @@
       <x:c r="V186" s="12"/>
       <x:c r="W186" s="9"/>
       <x:c r="X186" s="13"/>
+      <x:c r="Y186"/>
     </x:row>
     <x:row r="187">
       <x:c r="A187" s="10"/>
@@ -5416,6 +5608,7 @@
       <x:c r="V187" s="12"/>
       <x:c r="W187" s="9"/>
       <x:c r="X187" s="13"/>
+      <x:c r="Y187"/>
     </x:row>
     <x:row r="188">
       <x:c r="A188" s="10"/>
@@ -5442,6 +5635,7 @@
       <x:c r="V188" s="12"/>
       <x:c r="W188" s="9"/>
       <x:c r="X188" s="13"/>
+      <x:c r="Y188"/>
     </x:row>
     <x:row r="189">
       <x:c r="A189" s="10"/>
@@ -5468,6 +5662,7 @@
       <x:c r="V189" s="12"/>
       <x:c r="W189" s="9"/>
       <x:c r="X189" s="13"/>
+      <x:c r="Y189"/>
     </x:row>
     <x:row r="190">
       <x:c r="A190" s="10"/>
@@ -5494,6 +5689,7 @@
       <x:c r="V190" s="12"/>
       <x:c r="W190" s="9"/>
       <x:c r="X190" s="13"/>
+      <x:c r="Y190"/>
     </x:row>
     <x:row r="191">
       <x:c r="A191" s="10"/>
@@ -5520,6 +5716,7 @@
       <x:c r="V191" s="12"/>
       <x:c r="W191" s="9"/>
       <x:c r="X191" s="13"/>
+      <x:c r="Y191"/>
     </x:row>
     <x:row r="192">
       <x:c r="A192" s="10"/>
@@ -5546,6 +5743,7 @@
       <x:c r="V192" s="12"/>
       <x:c r="W192" s="9"/>
       <x:c r="X192" s="13"/>
+      <x:c r="Y192"/>
     </x:row>
     <x:row r="193">
       <x:c r="A193" s="10"/>
@@ -5572,6 +5770,7 @@
       <x:c r="V193" s="12"/>
       <x:c r="W193" s="9"/>
       <x:c r="X193" s="13"/>
+      <x:c r="Y193"/>
     </x:row>
     <x:row r="194">
       <x:c r="A194" s="10"/>
@@ -5598,6 +5797,7 @@
       <x:c r="V194" s="12"/>
       <x:c r="W194" s="9"/>
       <x:c r="X194" s="13"/>
+      <x:c r="Y194"/>
     </x:row>
     <x:row r="195">
       <x:c r="A195" s="10"/>
@@ -5624,6 +5824,7 @@
       <x:c r="V195" s="12"/>
       <x:c r="W195" s="9"/>
       <x:c r="X195" s="13"/>
+      <x:c r="Y195"/>
     </x:row>
     <x:row r="196">
       <x:c r="A196" s="10"/>
@@ -5650,6 +5851,7 @@
       <x:c r="V196" s="12"/>
       <x:c r="W196" s="9"/>
       <x:c r="X196" s="13"/>
+      <x:c r="Y196"/>
     </x:row>
     <x:row r="197">
       <x:c r="A197" s="10"/>
@@ -5676,6 +5878,7 @@
       <x:c r="V197" s="12"/>
       <x:c r="W197" s="9"/>
       <x:c r="X197" s="13"/>
+      <x:c r="Y197"/>
     </x:row>
     <x:row r="198">
       <x:c r="A198" s="10"/>
@@ -5702,6 +5905,7 @@
       <x:c r="V198" s="12"/>
       <x:c r="W198" s="9"/>
       <x:c r="X198" s="13"/>
+      <x:c r="Y198"/>
     </x:row>
     <x:row r="199">
       <x:c r="A199" s="10"/>
@@ -5728,6 +5932,7 @@
       <x:c r="V199" s="12"/>
       <x:c r="W199" s="9"/>
       <x:c r="X199" s="13"/>
+      <x:c r="Y199"/>
     </x:row>
     <x:row r="200">
       <x:c r="A200" s="10"/>
@@ -5754,6 +5959,7 @@
       <x:c r="V200" s="12"/>
       <x:c r="W200" s="9"/>
       <x:c r="X200" s="13"/>
+      <x:c r="Y200"/>
     </x:row>
     <x:row r="201">
       <x:c r="A201" s="10"/>
@@ -13625,7 +13831,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra87e7b7253cd49b3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R376740a757724565"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13867,6 +14073,14 @@
         <x:v>SĐT chủ nhà/người đăng — bắt buộc đối với SUPER_ADMIN.</x:v>
       </x:c>
     </x:row>
+    <x:row r="30">
+      <x:c r="A30" t="str">
+        <x:v>Ở chung với chủ nhà</x:v>
+      </x:c>
+      <x:c r="B30" t="str">
+        <x:v>Nhập Có nếu người thuê ở chung với chủ nhà; nhập Không nếu không ở chung; chưa xác định thì nhập Chưa rõ.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:B1"/>
